--- a/outputs/hhll_stocks.xlsx
+++ b/outputs/hhll_stocks.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rchak007\github\myTrading\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{29B693B6-1654-4A3B-B711-A81F5875A543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{87B5D536-9FEB-4407-8689-F9A7DA321D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{71314F9D-2700-45C5-9B08-2F1B9552D8C6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{862B9E86-E327-4B53-A387-1B375DD3D30A}"/>
   </bookViews>
   <sheets>
     <sheet name="hhll_stocks" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">hhll_stocks!$A$1:$N$121</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="145">
   <si>
     <t>Ticker</t>
   </si>
@@ -94,39 +97,39 @@
     <t>AEHR</t>
   </si>
   <si>
+    <t>ALAB</t>
+  </si>
+  <si>
+    <t>AMAT</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>BULLISH</t>
+  </si>
+  <si>
+    <t>HL</t>
+  </si>
+  <si>
+    <t>HH</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>APH</t>
+  </si>
+  <si>
+    <t>APLD</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
     <t>MIXED</t>
   </si>
   <si>
-    <t>HH</t>
-  </si>
-  <si>
-    <t>ALAB</t>
-  </si>
-  <si>
-    <t>AMAT</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>BULLISH</t>
-  </si>
-  <si>
-    <t>HL</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>APH</t>
-  </si>
-  <si>
-    <t>APLD</t>
-  </si>
-  <si>
-    <t>APP</t>
-  </si>
-  <si>
     <t>ARKB</t>
   </si>
   <si>
@@ -238,6 +241,9 @@
     <t>IBIT</t>
   </si>
   <si>
+    <t>IBM</t>
+  </si>
+  <si>
     <t>IDR</t>
   </si>
   <si>
@@ -298,6 +304,9 @@
     <t>MSTX</t>
   </si>
   <si>
+    <t>MTSI</t>
+  </si>
+  <si>
     <t>MU</t>
   </si>
   <si>
@@ -446,6 +455,9 @@
   </si>
   <si>
     <t>XLE</t>
+  </si>
+  <si>
+    <t>CHUCK COMMENTS</t>
   </si>
 </sst>
 </file>
@@ -588,7 +600,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -768,6 +780,24 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FF33"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -929,11 +959,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -981,6 +1015,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF66FF33"/>
+      <color rgb="FF00FFFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1308,20 +1348,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEEBF52-F251-4864-890A-D241890F76E8}">
-  <dimension ref="A1:N119"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FA06369-22C8-4AD5-8870-924992B3B984}">
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" customWidth="1"/>
+    <col min="15" max="15" width="39.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1364,8 +1399,11 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1373,7 +1411,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>315.32</v>
+        <v>313.5</v>
       </c>
       <c r="D2" t="s">
         <v>16</v>
@@ -1400,7 +1438,7 @@
         <v>317.39999999999998</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2">
         <v>17</v>
@@ -1408,8 +1446,9 @@
       <c r="N2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1417,7 +1456,7 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>119.92</v>
+        <v>122.56</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -1426,34 +1465,34 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
+        <v>127.51</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3">
         <v>110.5</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3">
-        <v>152.22999999999999</v>
       </c>
       <c r="J3">
         <v>110.5</v>
       </c>
       <c r="K3">
-        <v>152.22999999999999</v>
+        <v>127.51</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M3">
         <v>15</v>
       </c>
       <c r="N3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1461,7 +1500,7 @@
         <v>15</v>
       </c>
       <c r="C4">
-        <v>6.13</v>
+        <v>5.43</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -1470,31 +1509,31 @@
         <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
+        <v>6.65</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4">
         <v>10.199999999999999</v>
       </c>
-      <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4">
-        <v>13.88</v>
-      </c>
       <c r="K4">
-        <v>13.88</v>
+        <v>6.65</v>
       </c>
       <c r="L4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M4">
         <v>0</v>
       </c>
       <c r="N4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1502,154 +1541,154 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>72.599999999999994</v>
+        <v>70.849999999999994</v>
       </c>
       <c r="D5" t="s">
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
+        <v>79.489999999999995</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5">
         <v>63.32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5">
-        <v>126.62</v>
       </c>
       <c r="J5">
         <v>63.32</v>
       </c>
       <c r="K5">
-        <v>121.8</v>
+        <v>79.489999999999995</v>
       </c>
       <c r="L5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>19</v>
       </c>
       <c r="N5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>370.74</v>
+      </c>
+      <c r="D6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6">
+        <v>436.47</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6">
+        <v>366.66</v>
+      </c>
+      <c r="J6">
+        <v>316</v>
+      </c>
+      <c r="K6">
+        <v>436.47</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>12</v>
+      </c>
+      <c r="N6">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
-        <v>412.97</v>
-      </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>366.66</v>
-      </c>
-      <c r="H6" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="I6">
-        <v>499.48</v>
-      </c>
-      <c r="J6">
-        <v>372.5</v>
-      </c>
-      <c r="K6">
-        <v>499.48</v>
-      </c>
-      <c r="L6">
-        <v>63</v>
-      </c>
-      <c r="M6">
-        <v>14</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7">
-        <v>602.5</v>
+        <v>592.04</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7">
+        <v>629.98</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7">
         <v>527.63</v>
-      </c>
-      <c r="H7" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7">
-        <v>739.67</v>
       </c>
       <c r="J7">
         <v>527.63</v>
       </c>
       <c r="K7">
-        <v>739.67</v>
+        <v>629.98</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>24</v>
       </c>
       <c r="N7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8">
-        <v>557.89</v>
+        <v>560.41999999999996</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8">
         <v>498.15</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I8">
         <v>584.73</v>
@@ -1661,7 +1700,7 @@
         <v>584.73</v>
       </c>
       <c r="L8">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M8">
         <v>21</v>
@@ -1670,156 +1709,156 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9">
-        <v>245.34</v>
+        <v>245.56</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>249.71</v>
+        <v>251.03</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I9">
-        <v>225.55</v>
+        <v>238.25</v>
       </c>
       <c r="J9">
-        <v>225.55</v>
+        <v>238.25</v>
       </c>
       <c r="K9">
         <v>249.51</v>
       </c>
       <c r="L9">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>157.65</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10">
+        <v>164.89</v>
+      </c>
+      <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10">
+        <v>153.15</v>
+      </c>
+      <c r="J10">
+        <v>153.15</v>
+      </c>
+      <c r="K10">
+        <v>164.89</v>
+      </c>
+      <c r="L10">
+        <v>5</v>
+      </c>
+      <c r="M10">
+        <v>15</v>
+      </c>
+      <c r="N10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>28.19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11">
+        <v>33.56</v>
+      </c>
+      <c r="H11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11">
+        <v>29.93</v>
+      </c>
+      <c r="J11">
+        <v>20</v>
+      </c>
+      <c r="K11">
+        <v>33.56</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>159.06</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G10">
-        <v>153.15</v>
-      </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10">
-        <v>178.52</v>
-      </c>
-      <c r="J10">
-        <v>156.21</v>
-      </c>
-      <c r="K10">
-        <v>178.52</v>
-      </c>
-      <c r="L10">
-        <v>3</v>
-      </c>
-      <c r="M10">
-        <v>16</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>31.15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11">
-        <v>29.93</v>
-      </c>
-      <c r="H11" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11">
-        <v>49.34</v>
-      </c>
-      <c r="J11">
-        <v>30.51</v>
-      </c>
-      <c r="K11">
-        <v>46.87</v>
-      </c>
-      <c r="L11">
-        <v>8</v>
-      </c>
-      <c r="M11">
-        <v>12</v>
-      </c>
-      <c r="N11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>448.45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" t="s">
         <v>34</v>
       </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12">
-        <v>506.98</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" t="s">
-        <v>24</v>
-      </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G12">
         <v>576.46</v>
@@ -1831,22 +1870,22 @@
         <v>418.46</v>
       </c>
       <c r="J12">
-        <v>443</v>
+        <v>431.42</v>
       </c>
       <c r="K12">
         <v>576.46</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1854,10 +1893,10 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>21.2</v>
+        <v>21.42</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E13" t="s">
         <v>17</v>
@@ -1878,19 +1917,19 @@
         <v>19.239999999999998</v>
       </c>
       <c r="K13">
-        <v>21.29</v>
+        <v>22.31</v>
       </c>
       <c r="L13">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -1898,7 +1937,7 @@
         <v>15</v>
       </c>
       <c r="C14">
-        <v>323.39</v>
+        <v>280</v>
       </c>
       <c r="D14" t="s">
         <v>21</v>
@@ -1907,34 +1946,34 @@
         <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G14">
+        <v>339.44</v>
+      </c>
+      <c r="H14" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14">
         <v>290.45</v>
       </c>
-      <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14">
-        <v>361.95</v>
-      </c>
       <c r="J14">
-        <v>298.38</v>
+        <v>203.01</v>
       </c>
       <c r="K14">
-        <v>361.95</v>
+        <v>339.44</v>
       </c>
       <c r="L14">
+        <v>5</v>
+      </c>
+      <c r="M14">
+        <v>12</v>
+      </c>
+      <c r="N14">
         <v>3</v>
       </c>
-      <c r="M14">
-        <v>14</v>
-      </c>
-      <c r="N14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -1942,43 +1981,43 @@
         <v>15</v>
       </c>
       <c r="C15">
-        <v>1797.32</v>
+        <v>1776.75</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15">
+        <v>1858.73</v>
+      </c>
+      <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15">
         <v>1717.31</v>
       </c>
-      <c r="H15" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15">
-        <v>1999.96</v>
-      </c>
       <c r="J15">
-        <v>1730.29</v>
+        <v>1717.31</v>
       </c>
       <c r="K15">
-        <v>1999.96</v>
+        <v>1858.73</v>
       </c>
       <c r="L15">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -1986,7 +2025,7 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>73.319999999999993</v>
+        <v>69.67</v>
       </c>
       <c r="D16" t="s">
         <v>21</v>
@@ -2013,7 +2052,7 @@
         <v>91.82</v>
       </c>
       <c r="L16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M16">
         <v>11</v>
@@ -2030,16 +2069,16 @@
         <v>15</v>
       </c>
       <c r="C17">
-        <v>144.58000000000001</v>
+        <v>142.85</v>
       </c>
       <c r="D17" t="s">
         <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G17">
         <v>200.38</v>
@@ -2057,7 +2096,7 @@
         <v>200.38</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>3</v>
@@ -2074,40 +2113,40 @@
         <v>15</v>
       </c>
       <c r="C18">
-        <v>399.97</v>
+        <v>394.09</v>
       </c>
       <c r="D18" t="s">
         <v>16</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G18">
+        <v>407.52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18">
         <v>356.43</v>
-      </c>
-      <c r="H18" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18">
-        <v>379.62</v>
       </c>
       <c r="J18">
         <v>356.43</v>
       </c>
       <c r="K18">
-        <v>414.64</v>
+        <v>407.52</v>
       </c>
       <c r="L18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M18">
         <v>16</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2118,19 +2157,19 @@
         <v>15</v>
       </c>
       <c r="C19">
-        <v>112.33</v>
+        <v>112.75</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G19">
-        <v>99.46</v>
+        <v>115.58</v>
       </c>
       <c r="H19" t="s">
         <v>18</v>
@@ -2145,13 +2184,13 @@
         <v>113.82</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="M19">
         <v>4</v>
       </c>
       <c r="N19">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2162,16 +2201,16 @@
         <v>15</v>
       </c>
       <c r="C20">
-        <v>244.61</v>
+        <v>242.8</v>
       </c>
       <c r="D20" t="s">
         <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G20">
         <v>257.51</v>
@@ -2189,7 +2228,7 @@
         <v>320</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M20">
         <v>22</v>
@@ -2206,7 +2245,7 @@
         <v>15</v>
       </c>
       <c r="C21">
-        <v>57.56</v>
+        <v>57.34</v>
       </c>
       <c r="D21" t="s">
         <v>21</v>
@@ -2233,7 +2272,7 @@
         <v>66.239999999999995</v>
       </c>
       <c r="L21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M21">
         <v>12</v>
@@ -2250,16 +2289,16 @@
         <v>15</v>
       </c>
       <c r="C22">
-        <v>14.98</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G22">
         <v>14.1</v>
@@ -2277,7 +2316,7 @@
         <v>16.16</v>
       </c>
       <c r="L22">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M22">
         <v>3</v>
@@ -2294,7 +2333,7 @@
         <v>15</v>
       </c>
       <c r="C23">
-        <v>36.909999999999997</v>
+        <v>35.869999999999997</v>
       </c>
       <c r="D23" t="s">
         <v>21</v>
@@ -2303,31 +2342,31 @@
         <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23">
+        <v>37</v>
+      </c>
+      <c r="H23" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23">
         <v>35.56</v>
-      </c>
-      <c r="H23" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23">
-        <v>38.43</v>
       </c>
       <c r="J23">
         <v>35.78</v>
       </c>
       <c r="K23">
-        <v>38.369999999999997</v>
+        <v>37</v>
       </c>
       <c r="L23">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M23">
         <v>10</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -2338,7 +2377,7 @@
         <v>15</v>
       </c>
       <c r="C24">
-        <v>186</v>
+        <v>180.69</v>
       </c>
       <c r="D24" t="s">
         <v>21</v>
@@ -2359,16 +2398,16 @@
         <v>197.99</v>
       </c>
       <c r="J24">
-        <v>182.5</v>
+        <v>172.14</v>
       </c>
       <c r="K24">
         <v>197.99</v>
       </c>
       <c r="L24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N24">
         <v>6</v>
@@ -2382,7 +2421,7 @@
         <v>15</v>
       </c>
       <c r="C25">
-        <v>251.38</v>
+        <v>256.60000000000002</v>
       </c>
       <c r="D25" t="s">
         <v>21</v>
@@ -2409,7 +2448,7 @@
         <v>282.77</v>
       </c>
       <c r="L25">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M25">
         <v>3</v>
@@ -2426,13 +2465,13 @@
         <v>15</v>
       </c>
       <c r="C26">
-        <v>70.34</v>
+        <v>70.31</v>
       </c>
       <c r="D26" t="s">
         <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
         <v>18</v>
@@ -2441,7 +2480,7 @@
         <v>67.959999999999994</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I26">
         <v>72.94</v>
@@ -2453,7 +2492,7 @@
         <v>72.94</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M26">
         <v>19</v>
@@ -2470,40 +2509,40 @@
         <v>15</v>
       </c>
       <c r="C27">
-        <v>460.72</v>
+        <v>454.27</v>
       </c>
       <c r="D27" t="s">
         <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G27">
+        <v>485.69</v>
+      </c>
+      <c r="H27" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27">
         <v>404.43</v>
-      </c>
-      <c r="H27" t="s">
-        <v>25</v>
-      </c>
-      <c r="I27">
-        <v>494.53</v>
       </c>
       <c r="J27">
         <v>417.34</v>
       </c>
       <c r="K27">
-        <v>494.53</v>
+        <v>485.69</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>22</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2514,13 +2553,13 @@
         <v>15</v>
       </c>
       <c r="C28">
-        <v>12.85</v>
+        <v>13.57</v>
       </c>
       <c r="D28" t="s">
         <v>21</v>
       </c>
       <c r="E28" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F28" t="s">
         <v>18</v>
@@ -2529,22 +2568,22 @@
         <v>11.94</v>
       </c>
       <c r="H28" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I28">
         <v>19.05</v>
       </c>
       <c r="J28">
-        <v>12.4</v>
+        <v>11.94</v>
       </c>
       <c r="K28">
         <v>18.100000000000001</v>
       </c>
       <c r="L28">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>5</v>
@@ -2558,7 +2597,7 @@
         <v>15</v>
       </c>
       <c r="C29">
-        <v>159.07</v>
+        <v>158.01</v>
       </c>
       <c r="D29" t="s">
         <v>21</v>
@@ -2585,7 +2624,7 @@
         <v>173.09</v>
       </c>
       <c r="L29">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M29">
         <v>2</v>
@@ -2602,7 +2641,7 @@
         <v>15</v>
       </c>
       <c r="C30">
-        <v>324.5</v>
+        <v>312</v>
       </c>
       <c r="D30" t="s">
         <v>21</v>
@@ -2611,31 +2650,31 @@
         <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G30">
+        <v>340.73</v>
+      </c>
+      <c r="H30" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30">
         <v>304.07</v>
       </c>
-      <c r="H30" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30">
-        <v>399.45</v>
-      </c>
       <c r="J30">
-        <v>308.17</v>
+        <v>304.07</v>
       </c>
       <c r="K30">
-        <v>399.45</v>
+        <v>340.73</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N30">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2646,7 +2685,7 @@
         <v>15</v>
       </c>
       <c r="C31">
-        <v>76.540000000000006</v>
+        <v>78.069999999999993</v>
       </c>
       <c r="D31" t="s">
         <v>21</v>
@@ -2673,7 +2712,7 @@
         <v>78.63</v>
       </c>
       <c r="L31">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M31">
         <v>15</v>
@@ -2690,40 +2729,40 @@
         <v>15</v>
       </c>
       <c r="C32">
-        <v>23.49</v>
+        <v>22.29</v>
       </c>
       <c r="D32" t="s">
         <v>21</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G32">
+        <v>24.65</v>
+      </c>
+      <c r="H32" t="s">
+        <v>18</v>
+      </c>
+      <c r="I32">
         <v>20.71</v>
-      </c>
-      <c r="H32" t="s">
-        <v>25</v>
-      </c>
-      <c r="I32">
-        <v>30.43</v>
       </c>
       <c r="J32">
         <v>20.81</v>
       </c>
       <c r="K32">
-        <v>30.43</v>
+        <v>24.65</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>17</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -2734,25 +2773,25 @@
         <v>15</v>
       </c>
       <c r="C33">
-        <v>66.14</v>
+        <v>62.61</v>
       </c>
       <c r="D33" t="s">
         <v>21</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F33" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G33">
-        <v>69.98</v>
+        <v>72.86</v>
       </c>
       <c r="H33" t="s">
         <v>18</v>
       </c>
       <c r="I33">
-        <v>61.77</v>
+        <v>61.67</v>
       </c>
       <c r="J33">
         <v>61.77</v>
@@ -2761,13 +2800,13 @@
         <v>69.98</v>
       </c>
       <c r="L33">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M33">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N33">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -2778,7 +2817,7 @@
         <v>15</v>
       </c>
       <c r="C34">
-        <v>257.79000000000002</v>
+        <v>241.63</v>
       </c>
       <c r="D34" t="s">
         <v>21</v>
@@ -2805,7 +2844,7 @@
         <v>280.5</v>
       </c>
       <c r="L34">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M34">
         <v>14</v>
@@ -2822,7 +2861,7 @@
         <v>15</v>
       </c>
       <c r="C35">
-        <v>88.88</v>
+        <v>80.459999999999994</v>
       </c>
       <c r="D35" t="s">
         <v>21</v>
@@ -2831,31 +2870,31 @@
         <v>17</v>
       </c>
       <c r="F35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G35">
+        <v>95.14</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35">
         <v>79.459999999999994</v>
-      </c>
-      <c r="H35" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35">
-        <v>122</v>
       </c>
       <c r="J35">
         <v>79.459999999999994</v>
       </c>
       <c r="K35">
-        <v>122</v>
+        <v>95.14</v>
       </c>
       <c r="L35">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M35">
         <v>4</v>
       </c>
       <c r="N35">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -2866,22 +2905,22 @@
         <v>15</v>
       </c>
       <c r="C36">
-        <v>187.18</v>
+        <v>205.83</v>
       </c>
       <c r="D36" t="s">
         <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G36">
         <v>185.3</v>
       </c>
       <c r="H36" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I36">
         <v>209.5</v>
@@ -2893,7 +2932,7 @@
         <v>209.5</v>
       </c>
       <c r="L36">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M36">
         <v>11</v>
@@ -2910,37 +2949,37 @@
         <v>15</v>
       </c>
       <c r="C37">
-        <v>85.68</v>
+        <v>85.49</v>
       </c>
       <c r="D37" t="s">
         <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F37" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G37">
+        <v>83.23</v>
+      </c>
+      <c r="H37" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37">
         <v>87.69</v>
       </c>
-      <c r="H37" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37">
-        <v>74.42</v>
-      </c>
       <c r="J37">
-        <v>74.42</v>
+        <v>83.23</v>
       </c>
       <c r="K37">
         <v>87.69</v>
       </c>
       <c r="L37">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M37">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N37">
         <v>1</v>
@@ -2954,40 +2993,40 @@
         <v>15</v>
       </c>
       <c r="C38">
-        <v>434.97</v>
+        <v>457.62</v>
       </c>
       <c r="D38" t="s">
         <v>16</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G38">
+        <v>460.5</v>
+      </c>
+      <c r="H38" t="s">
+        <v>28</v>
+      </c>
+      <c r="I38">
         <v>386.01</v>
-      </c>
-      <c r="H38" t="s">
-        <v>19</v>
-      </c>
-      <c r="I38">
-        <v>438.52</v>
       </c>
       <c r="J38">
         <v>386.01</v>
       </c>
       <c r="K38">
-        <v>469.47</v>
+        <v>460.5</v>
       </c>
       <c r="L38">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M38">
         <v>20</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
@@ -2998,13 +3037,13 @@
         <v>15</v>
       </c>
       <c r="C39">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="D39" t="s">
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F39" t="s">
         <v>18</v>
@@ -3013,22 +3052,22 @@
         <v>4.67</v>
       </c>
       <c r="H39" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I39">
         <v>6.1</v>
       </c>
       <c r="J39">
-        <v>4.67</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="K39">
         <v>6.03</v>
       </c>
       <c r="L39">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M39">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>8</v>
@@ -3042,16 +3081,16 @@
         <v>15</v>
       </c>
       <c r="C40">
-        <v>13.53</v>
+        <v>14.14</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G40">
         <v>12.91</v>
@@ -3066,16 +3105,16 @@
         <v>12.91</v>
       </c>
       <c r="K40">
-        <v>13.67</v>
+        <v>16.25</v>
       </c>
       <c r="L40">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M40">
         <v>5</v>
       </c>
       <c r="N40">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
@@ -3086,40 +3125,40 @@
         <v>15</v>
       </c>
       <c r="C41">
-        <v>21.11</v>
+        <v>24.2</v>
       </c>
       <c r="D41" t="s">
         <v>16</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G41">
+        <v>20.440000000000001</v>
+      </c>
+      <c r="H41" t="s">
+        <v>29</v>
+      </c>
+      <c r="I41">
         <v>23.42</v>
       </c>
-      <c r="H41" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41">
-        <v>16.8</v>
-      </c>
       <c r="J41">
-        <v>16.8</v>
+        <v>20.440000000000001</v>
       </c>
       <c r="K41">
-        <v>23.42</v>
+        <v>27.74</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -3130,40 +3169,40 @@
         <v>15</v>
       </c>
       <c r="C42">
-        <v>1091.57</v>
+        <v>1064.74</v>
       </c>
       <c r="D42" t="s">
         <v>16</v>
       </c>
       <c r="E42" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G42">
+        <v>1115.07</v>
+      </c>
+      <c r="H42" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42">
         <v>1028</v>
-      </c>
-      <c r="H42" t="s">
-        <v>25</v>
-      </c>
-      <c r="I42">
-        <v>1195.94</v>
       </c>
       <c r="J42">
         <v>1028</v>
       </c>
       <c r="K42">
-        <v>1181.3499999999999</v>
+        <v>1115.07</v>
       </c>
       <c r="L42">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M42">
         <v>23</v>
       </c>
       <c r="N42">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -3174,16 +3213,16 @@
         <v>15</v>
       </c>
       <c r="C43">
-        <v>377.01</v>
+        <v>373.15</v>
       </c>
       <c r="D43" t="s">
         <v>21</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F43" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G43">
         <v>368.95</v>
@@ -3195,16 +3234,16 @@
         <v>383.6</v>
       </c>
       <c r="J43">
-        <v>368.95</v>
+        <v>363.32</v>
       </c>
       <c r="K43">
         <v>383.6</v>
       </c>
       <c r="L43">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M43">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N43">
         <v>9</v>
@@ -3218,40 +3257,40 @@
         <v>15</v>
       </c>
       <c r="C44">
-        <v>24.88</v>
+        <v>23.73</v>
       </c>
       <c r="D44" t="s">
         <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G44">
+        <v>26.66</v>
+      </c>
+      <c r="H44" t="s">
+        <v>18</v>
+      </c>
+      <c r="I44">
         <v>23.29</v>
       </c>
-      <c r="H44" t="s">
-        <v>25</v>
-      </c>
-      <c r="I44">
-        <v>36.1</v>
-      </c>
       <c r="J44">
-        <v>24.05</v>
+        <v>23.29</v>
       </c>
       <c r="K44">
-        <v>34.729999999999997</v>
+        <v>26.66</v>
       </c>
       <c r="L44">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N44">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -3262,37 +3301,37 @@
         <v>15</v>
       </c>
       <c r="C45">
-        <v>355.03</v>
+        <v>353.77</v>
       </c>
       <c r="D45" t="s">
         <v>21</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F45" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G45">
+        <v>348.66</v>
+      </c>
+      <c r="H45" t="s">
+        <v>19</v>
+      </c>
+      <c r="I45">
         <v>370.89</v>
       </c>
-      <c r="H45" t="s">
-        <v>18</v>
-      </c>
-      <c r="I45">
-        <v>333.69</v>
-      </c>
       <c r="J45">
-        <v>333.69</v>
+        <v>348.66</v>
       </c>
       <c r="K45">
         <v>370.89</v>
       </c>
       <c r="L45">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M45">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N45">
         <v>4</v>
@@ -3306,37 +3345,37 @@
         <v>15</v>
       </c>
       <c r="C46">
-        <v>34.380000000000003</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="D46" t="s">
         <v>16</v>
       </c>
       <c r="E46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46">
+        <v>33.18</v>
+      </c>
+      <c r="H46" t="s">
         <v>29</v>
       </c>
-      <c r="F46" t="s">
-        <v>25</v>
-      </c>
-      <c r="G46">
+      <c r="I46">
         <v>39.049999999999997</v>
       </c>
-      <c r="H46" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46">
-        <v>30.29</v>
-      </c>
       <c r="J46">
-        <v>30.29</v>
+        <v>33.18</v>
       </c>
       <c r="K46">
         <v>39.049999999999997</v>
       </c>
       <c r="L46">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N46">
         <v>7</v>
@@ -3350,10 +3389,10 @@
         <v>15</v>
       </c>
       <c r="C47">
-        <v>18.079999999999998</v>
+        <v>18.27</v>
       </c>
       <c r="D47" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E47" t="s">
         <v>17</v>
@@ -3374,16 +3413,16 @@
         <v>16.399999999999999</v>
       </c>
       <c r="K47">
-        <v>18.16</v>
+        <v>19.02</v>
       </c>
       <c r="L47">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M47">
         <v>1</v>
       </c>
       <c r="N47">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -3394,37 +3433,37 @@
         <v>15</v>
       </c>
       <c r="C48">
-        <v>111.97</v>
+        <v>109.84</v>
       </c>
       <c r="D48" t="s">
         <v>16</v>
       </c>
       <c r="E48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48">
+        <v>108.81</v>
+      </c>
+      <c r="H48" t="s">
         <v>29</v>
       </c>
-      <c r="F48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G48">
+      <c r="I48">
         <v>120.05</v>
       </c>
-      <c r="H48" t="s">
-        <v>30</v>
-      </c>
-      <c r="I48">
-        <v>92.8</v>
-      </c>
       <c r="J48">
-        <v>92.8</v>
+        <v>108.81</v>
       </c>
       <c r="K48">
         <v>120.05</v>
       </c>
       <c r="L48">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M48">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N48">
         <v>9</v>
@@ -3438,10 +3477,10 @@
         <v>15</v>
       </c>
       <c r="C49">
-        <v>36.229999999999997</v>
+        <v>36.619999999999997</v>
       </c>
       <c r="D49" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E49" t="s">
         <v>17</v>
@@ -3462,16 +3501,16 @@
         <v>32.840000000000003</v>
       </c>
       <c r="K49">
-        <v>36.369999999999997</v>
+        <v>38.1</v>
       </c>
       <c r="L49">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M49">
         <v>1</v>
       </c>
       <c r="N49">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -3482,40 +3521,40 @@
         <v>15</v>
       </c>
       <c r="C50">
-        <v>30.76</v>
+        <v>215.4</v>
       </c>
       <c r="D50" t="s">
         <v>21</v>
       </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F50" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G50">
-        <v>28.9</v>
+        <v>284.44</v>
       </c>
       <c r="H50" t="s">
         <v>19</v>
       </c>
       <c r="I50">
-        <v>35</v>
+        <v>311.8</v>
       </c>
       <c r="J50">
-        <v>28.9</v>
+        <v>212.34</v>
       </c>
       <c r="K50">
-        <v>35</v>
+        <v>311.8</v>
       </c>
       <c r="L50">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M50">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -3526,7 +3565,7 @@
         <v>15</v>
       </c>
       <c r="C51">
-        <v>67.8</v>
+        <v>30.89</v>
       </c>
       <c r="D51" t="s">
         <v>21</v>
@@ -3535,31 +3574,31 @@
         <v>17</v>
       </c>
       <c r="F51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G51">
-        <v>67.099999999999994</v>
+        <v>31.79</v>
       </c>
       <c r="H51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I51">
-        <v>77.569999999999993</v>
+        <v>28.9</v>
       </c>
       <c r="J51">
-        <v>67.099999999999994</v>
+        <v>28.9</v>
       </c>
       <c r="K51">
-        <v>77.569999999999993</v>
+        <v>31.79</v>
       </c>
       <c r="L51">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="M51">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -3570,7 +3609,7 @@
         <v>15</v>
       </c>
       <c r="C52">
-        <v>22.24</v>
+        <v>67.14</v>
       </c>
       <c r="D52" t="s">
         <v>21</v>
@@ -3582,28 +3621,28 @@
         <v>19</v>
       </c>
       <c r="G52">
-        <v>22.73</v>
+        <v>71.680000000000007</v>
       </c>
       <c r="H52" t="s">
         <v>18</v>
       </c>
       <c r="I52">
-        <v>21.7</v>
+        <v>66</v>
       </c>
       <c r="J52">
-        <v>21.7</v>
+        <v>66</v>
       </c>
       <c r="K52">
-        <v>22.73</v>
+        <v>71.680000000000007</v>
       </c>
       <c r="L52">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M52">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N52">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -3614,7 +3653,7 @@
         <v>15</v>
       </c>
       <c r="C53">
-        <v>42.86</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
         <v>21</v>
@@ -3626,25 +3665,25 @@
         <v>19</v>
       </c>
       <c r="G53">
-        <v>54.84</v>
+        <v>22.73</v>
       </c>
       <c r="H53" t="s">
         <v>18</v>
       </c>
       <c r="I53">
-        <v>48.49</v>
+        <v>21.7</v>
       </c>
       <c r="J53">
-        <v>39.76</v>
+        <v>21.7</v>
       </c>
       <c r="K53">
-        <v>54.84</v>
+        <v>22.73</v>
       </c>
       <c r="L53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M53">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N53">
         <v>6</v>
@@ -3658,40 +3697,40 @@
         <v>15</v>
       </c>
       <c r="C54">
-        <v>50.06</v>
+        <v>39.04</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E54" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F54" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G54">
-        <v>57.18</v>
+        <v>54.84</v>
       </c>
       <c r="H54" t="s">
         <v>18</v>
       </c>
       <c r="I54">
-        <v>40.6</v>
+        <v>48.49</v>
       </c>
       <c r="J54">
-        <v>40.6</v>
+        <v>26.33</v>
       </c>
       <c r="K54">
-        <v>57.18</v>
+        <v>54.84</v>
       </c>
       <c r="L54">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M54">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -3702,40 +3741,40 @@
         <v>15</v>
       </c>
       <c r="C55">
-        <v>41.14</v>
+        <v>49.24</v>
       </c>
       <c r="D55" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E55" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G55">
-        <v>44.97</v>
+        <v>57.18</v>
       </c>
       <c r="H55" t="s">
         <v>18</v>
       </c>
       <c r="I55">
-        <v>37.659999999999997</v>
+        <v>40.6</v>
       </c>
       <c r="J55">
-        <v>37.659999999999997</v>
+        <v>40.6</v>
       </c>
       <c r="K55">
-        <v>44.97</v>
+        <v>57.18</v>
       </c>
       <c r="L55">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="M55">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -3746,7 +3785,7 @@
         <v>15</v>
       </c>
       <c r="C56">
-        <v>48.19</v>
+        <v>38.229999999999997</v>
       </c>
       <c r="D56" t="s">
         <v>21</v>
@@ -3758,28 +3797,28 @@
         <v>19</v>
       </c>
       <c r="G56">
-        <v>58.88</v>
+        <v>45.54</v>
       </c>
       <c r="H56" t="s">
         <v>18</v>
       </c>
       <c r="I56">
-        <v>46.01</v>
+        <v>37.659999999999997</v>
       </c>
       <c r="J56">
-        <v>46.01</v>
+        <v>37.659999999999997</v>
       </c>
       <c r="K56">
-        <v>58.88</v>
+        <v>45.54</v>
       </c>
       <c r="L56">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M56">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N56">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -3790,40 +3829,40 @@
         <v>15</v>
       </c>
       <c r="C57">
-        <v>171.05</v>
+        <v>48.94</v>
       </c>
       <c r="D57" t="s">
         <v>21</v>
       </c>
       <c r="E57" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F57" t="s">
         <v>19</v>
       </c>
       <c r="G57">
-        <v>179.82</v>
+        <v>58.88</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I57">
-        <v>156.35</v>
+        <v>46.01</v>
       </c>
       <c r="J57">
-        <v>156.35</v>
+        <v>46.01</v>
       </c>
       <c r="K57">
-        <v>179.82</v>
+        <v>58.88</v>
       </c>
       <c r="L57">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M57">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N57">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -3834,40 +3873,40 @@
         <v>15</v>
       </c>
       <c r="C58">
-        <v>802.01</v>
+        <v>158.5</v>
       </c>
       <c r="D58" t="s">
         <v>21</v>
       </c>
       <c r="E58" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G58">
-        <v>680.43</v>
+        <v>179.82</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I58">
-        <v>874.86</v>
+        <v>156.35</v>
       </c>
       <c r="J58">
-        <v>680.43</v>
+        <v>144.65</v>
       </c>
       <c r="K58">
-        <v>874.86</v>
+        <v>179.82</v>
       </c>
       <c r="L58">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M58">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -3878,40 +3917,40 @@
         <v>15</v>
       </c>
       <c r="C59">
-        <v>523.22</v>
+        <v>813.4</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E59" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G59">
-        <v>547.47</v>
+        <v>680.43</v>
       </c>
       <c r="H59" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I59">
-        <v>498.3</v>
+        <v>874.86</v>
       </c>
       <c r="J59">
-        <v>498.3</v>
+        <v>680.43</v>
       </c>
       <c r="K59">
-        <v>547.47</v>
+        <v>874.86</v>
       </c>
       <c r="L59">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="M59">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -3922,40 +3961,40 @@
         <v>15</v>
       </c>
       <c r="C60">
-        <v>350.33</v>
+        <v>522.78</v>
       </c>
       <c r="D60" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E60" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F60" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G60">
-        <v>313.10000000000002</v>
+        <v>513.80999999999995</v>
       </c>
       <c r="H60" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I60">
-        <v>438.5</v>
+        <v>547.47</v>
       </c>
       <c r="J60">
-        <v>313.10000000000002</v>
+        <v>513.80999999999995</v>
       </c>
       <c r="K60">
-        <v>438.5</v>
+        <v>547.47</v>
       </c>
       <c r="L60">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M60">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -3966,7 +4005,7 @@
         <v>15</v>
       </c>
       <c r="C61">
-        <v>8.42</v>
+        <v>345.32</v>
       </c>
       <c r="D61" t="s">
         <v>21</v>
@@ -3975,31 +4014,31 @@
         <v>17</v>
       </c>
       <c r="F61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G61">
-        <v>7.9</v>
+        <v>369.95</v>
       </c>
       <c r="H61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I61">
-        <v>9.43</v>
+        <v>313.10000000000002</v>
       </c>
       <c r="J61">
-        <v>7.9</v>
+        <v>313.10000000000002</v>
       </c>
       <c r="K61">
-        <v>9.43</v>
+        <v>369.95</v>
       </c>
       <c r="L61">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="M61">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="N61">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -4010,7 +4049,7 @@
         <v>15</v>
       </c>
       <c r="C62">
-        <v>16.14</v>
+        <v>7.87</v>
       </c>
       <c r="D62" t="s">
         <v>21</v>
@@ -4019,31 +4058,31 @@
         <v>17</v>
       </c>
       <c r="F62" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G62">
-        <v>16.170000000000002</v>
+        <v>8.75</v>
       </c>
       <c r="H62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I62">
-        <v>22.5</v>
+        <v>7.9</v>
       </c>
       <c r="J62">
-        <v>15.85</v>
+        <v>6.85</v>
       </c>
       <c r="K62">
-        <v>22.5</v>
+        <v>8.75</v>
       </c>
       <c r="L62">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="M62">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -4054,40 +4093,40 @@
         <v>15</v>
       </c>
       <c r="C63">
-        <v>669.21</v>
+        <v>15.24</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E63" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="H63" t="s">
+        <v>19</v>
+      </c>
+      <c r="I63">
+        <v>22.5</v>
+      </c>
+      <c r="J63">
+        <v>14.54</v>
+      </c>
+      <c r="K63">
+        <v>22.5</v>
+      </c>
+      <c r="L63">
         <v>25</v>
       </c>
-      <c r="G63">
-        <v>628.28</v>
-      </c>
-      <c r="H63" t="s">
-        <v>18</v>
-      </c>
-      <c r="I63">
-        <v>540.17999999999995</v>
-      </c>
-      <c r="J63">
-        <v>540.17999999999995</v>
-      </c>
-      <c r="K63">
-        <v>681.87</v>
-      </c>
-      <c r="L63">
-        <v>6</v>
-      </c>
       <c r="M63">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="N63">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -4098,40 +4137,40 @@
         <v>15</v>
       </c>
       <c r="C64">
-        <v>97.39</v>
+        <v>656.66</v>
       </c>
       <c r="D64" t="s">
         <v>16</v>
       </c>
       <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s">
         <v>29</v>
       </c>
-      <c r="F64" t="s">
-        <v>25</v>
-      </c>
       <c r="G64">
-        <v>99.15</v>
+        <v>677.86</v>
       </c>
       <c r="H64" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I64">
-        <v>95.1</v>
+        <v>577.07000000000005</v>
       </c>
       <c r="J64">
-        <v>95.1</v>
+        <v>577.07000000000005</v>
       </c>
       <c r="K64">
-        <v>97.87</v>
+        <v>677.86</v>
       </c>
       <c r="L64">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="M64">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -4142,40 +4181,40 @@
         <v>15</v>
       </c>
       <c r="C65">
-        <v>52.21</v>
+        <v>97.83</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E65" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F65" t="s">
         <v>18</v>
       </c>
       <c r="G65">
-        <v>49.25</v>
+        <v>94.73</v>
       </c>
       <c r="H65" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I65">
-        <v>57.46</v>
+        <v>99.15</v>
       </c>
       <c r="J65">
-        <v>49.25</v>
+        <v>95.1</v>
       </c>
       <c r="K65">
-        <v>57.46</v>
+        <v>97.87</v>
       </c>
       <c r="L65">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="M65">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="N65">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -4186,7 +4225,7 @@
         <v>15</v>
       </c>
       <c r="C66">
-        <v>235.81</v>
+        <v>50.84</v>
       </c>
       <c r="D66" t="s">
         <v>21</v>
@@ -4195,31 +4234,31 @@
         <v>17</v>
       </c>
       <c r="F66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G66">
-        <v>222.89</v>
+        <v>54.3</v>
       </c>
       <c r="H66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I66">
-        <v>299.93</v>
+        <v>49.25</v>
       </c>
       <c r="J66">
-        <v>222.89</v>
+        <v>49.25</v>
       </c>
       <c r="K66">
-        <v>299.93</v>
+        <v>54.3</v>
       </c>
       <c r="L66">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="M66">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -4230,7 +4269,7 @@
         <v>15</v>
       </c>
       <c r="C67">
-        <v>385.1</v>
+        <v>223.4</v>
       </c>
       <c r="D67" t="s">
         <v>21</v>
@@ -4242,28 +4281,28 @@
         <v>19</v>
       </c>
       <c r="G67">
-        <v>395.57</v>
+        <v>251.64</v>
       </c>
       <c r="H67" t="s">
         <v>18</v>
       </c>
       <c r="I67">
-        <v>349.2</v>
+        <v>222.89</v>
       </c>
       <c r="J67">
-        <v>352.21</v>
+        <v>194.65</v>
       </c>
       <c r="K67">
-        <v>395.57</v>
+        <v>251.64</v>
       </c>
       <c r="L67">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="N67">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -4274,40 +4313,40 @@
         <v>15</v>
       </c>
       <c r="C68">
-        <v>94.64</v>
+        <v>384.77</v>
       </c>
       <c r="D68" t="s">
         <v>21</v>
       </c>
       <c r="E68" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F68" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G68">
-        <v>91.78</v>
+        <v>373.35</v>
       </c>
       <c r="H68" t="s">
         <v>19</v>
       </c>
       <c r="I68">
-        <v>104.78</v>
+        <v>395.57</v>
       </c>
       <c r="J68">
-        <v>91.78</v>
+        <v>373.35</v>
       </c>
       <c r="K68">
-        <v>104.78</v>
+        <v>395.57</v>
       </c>
       <c r="L68">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -4318,40 +4357,40 @@
         <v>15</v>
       </c>
       <c r="C69">
-        <v>8.6</v>
+        <v>96.58</v>
       </c>
       <c r="D69" t="s">
         <v>21</v>
       </c>
       <c r="E69" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F69" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G69">
-        <v>8.1</v>
+        <v>100.12</v>
       </c>
       <c r="H69" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I69">
-        <v>10.58</v>
+        <v>91.78</v>
       </c>
       <c r="J69">
-        <v>8.1</v>
+        <v>91.78</v>
       </c>
       <c r="K69">
-        <v>10.58</v>
+        <v>100.12</v>
       </c>
       <c r="L69">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M69">
         <v>2</v>
       </c>
       <c r="N69">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -4362,40 +4401,40 @@
         <v>15</v>
       </c>
       <c r="C70">
-        <v>979.3</v>
+        <v>8.93</v>
       </c>
       <c r="D70" t="s">
         <v>21</v>
       </c>
       <c r="E70" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F70" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G70">
-        <v>891.66</v>
+        <v>9.6</v>
       </c>
       <c r="H70" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I70">
-        <v>1254.81</v>
+        <v>8.1</v>
       </c>
       <c r="J70">
-        <v>891.66</v>
+        <v>8.1</v>
       </c>
       <c r="K70">
-        <v>1213.3699999999999</v>
+        <v>9.6</v>
       </c>
       <c r="L70">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="M70">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -4406,40 +4445,40 @@
         <v>15</v>
       </c>
       <c r="C71">
-        <v>91.3</v>
+        <v>304.72000000000003</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E71" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G71">
-        <v>78.099999999999994</v>
+        <v>328.62</v>
       </c>
       <c r="H71" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I71">
-        <v>128.30000000000001</v>
+        <v>297.23</v>
       </c>
       <c r="J71">
-        <v>82.21</v>
+        <v>260.85000000000002</v>
       </c>
       <c r="K71">
-        <v>128.30000000000001</v>
+        <v>328.62</v>
       </c>
       <c r="L71">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M71">
         <v>17</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -4450,7 +4489,7 @@
         <v>15</v>
       </c>
       <c r="C72">
-        <v>219.65</v>
+        <v>981.32</v>
       </c>
       <c r="D72" t="s">
         <v>21</v>
@@ -4459,31 +4498,31 @@
         <v>17</v>
       </c>
       <c r="F72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G72">
-        <v>192.67</v>
+        <v>1035.5</v>
       </c>
       <c r="H72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I72">
-        <v>290.60000000000002</v>
+        <v>891.66</v>
       </c>
       <c r="J72">
-        <v>192.67</v>
+        <v>891.66</v>
       </c>
       <c r="K72">
-        <v>290.60000000000002</v>
+        <v>1035.5</v>
       </c>
       <c r="L72">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M72">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N72">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
@@ -4494,40 +4533,40 @@
         <v>15</v>
       </c>
       <c r="C73">
-        <v>82.09</v>
+        <v>92.64</v>
       </c>
       <c r="D73" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E73" t="s">
         <v>17</v>
       </c>
       <c r="F73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G73">
-        <v>75.540000000000006</v>
+        <v>97.25</v>
       </c>
       <c r="H73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I73">
-        <v>86</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="J73">
-        <v>75.540000000000006</v>
+        <v>82.21</v>
       </c>
       <c r="K73">
-        <v>86</v>
+        <v>97.25</v>
       </c>
       <c r="L73">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M73">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -4538,40 +4577,40 @@
         <v>15</v>
       </c>
       <c r="C74">
-        <v>87.96</v>
+        <v>198.63</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F74" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G74">
-        <v>89.25</v>
+        <v>229.5</v>
       </c>
       <c r="H74" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I74">
-        <v>86.32</v>
+        <v>192.67</v>
       </c>
       <c r="J74">
-        <v>86.32</v>
+        <v>192.67</v>
       </c>
       <c r="K74">
-        <v>89.19</v>
+        <v>229.5</v>
       </c>
       <c r="L74">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M74">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
@@ -4582,40 +4621,40 @@
         <v>15</v>
       </c>
       <c r="C75">
-        <v>268.39999999999998</v>
+        <v>84.1</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G75">
-        <v>238.9</v>
+        <v>75.540000000000006</v>
       </c>
       <c r="H75" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I75">
-        <v>252.35</v>
+        <v>86</v>
       </c>
       <c r="J75">
-        <v>238.9</v>
+        <v>75.540000000000006</v>
       </c>
       <c r="K75">
-        <v>276.82</v>
+        <v>86</v>
       </c>
       <c r="L75">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M75">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
@@ -4626,40 +4665,40 @@
         <v>15</v>
       </c>
       <c r="C76">
-        <v>539.63</v>
+        <v>89.46</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E76" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F76" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G76">
-        <v>552.63</v>
+        <v>86.84</v>
       </c>
       <c r="H76" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I76">
-        <v>493.84</v>
+        <v>89.25</v>
       </c>
       <c r="J76">
-        <v>493.84</v>
+        <v>86.84</v>
       </c>
       <c r="K76">
-        <v>552.63</v>
+        <v>95.1</v>
       </c>
       <c r="L76">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M76">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N76">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
@@ -4670,40 +4709,37 @@
         <v>15</v>
       </c>
       <c r="C77">
-        <v>124.69</v>
+        <v>283</v>
       </c>
       <c r="D77" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F77" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G77">
-        <v>126.7</v>
+        <v>238.9</v>
       </c>
       <c r="H77" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I77">
-        <v>121.57</v>
+        <v>252.35</v>
       </c>
       <c r="J77">
-        <v>122.91</v>
-      </c>
-      <c r="K77">
-        <v>126.7</v>
+        <v>238.9</v>
       </c>
       <c r="L77">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="M77">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N77">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -4714,40 +4750,40 @@
         <v>15</v>
       </c>
       <c r="C78">
-        <v>0.43</v>
+        <v>537</v>
       </c>
       <c r="D78" t="s">
         <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F78" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G78">
-        <v>0.28999999999999998</v>
+        <v>528.02</v>
       </c>
       <c r="H78" t="s">
         <v>19</v>
       </c>
       <c r="I78">
-        <v>0.49</v>
+        <v>552.63</v>
       </c>
       <c r="J78">
-        <v>0.4</v>
+        <v>528.02</v>
       </c>
       <c r="K78">
-        <v>0.49</v>
+        <v>552.63</v>
       </c>
       <c r="L78">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M78">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N78">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
@@ -4758,40 +4794,40 @@
         <v>15</v>
       </c>
       <c r="C79">
-        <v>210.96</v>
+        <v>123.17</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E79" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F79" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G79">
-        <v>191.14</v>
+        <v>126.7</v>
       </c>
       <c r="H79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I79">
-        <v>200.63</v>
+        <v>121.57</v>
       </c>
       <c r="J79">
-        <v>191.14</v>
+        <v>122.91</v>
       </c>
       <c r="K79">
-        <v>212.71</v>
+        <v>126.7</v>
       </c>
       <c r="L79">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="M79">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N79">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
@@ -4802,7 +4838,7 @@
         <v>15</v>
       </c>
       <c r="C80">
-        <v>48.85</v>
+        <v>0.41</v>
       </c>
       <c r="D80" t="s">
         <v>21</v>
@@ -4814,28 +4850,28 @@
         <v>18</v>
       </c>
       <c r="G80">
-        <v>45.83</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="H80" t="s">
         <v>19</v>
       </c>
       <c r="I80">
-        <v>56.34</v>
+        <v>0.49</v>
       </c>
       <c r="J80">
-        <v>45.83</v>
+        <v>0.4</v>
       </c>
       <c r="K80">
-        <v>56.34</v>
+        <v>0.49</v>
       </c>
       <c r="L80">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M80">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N80">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
@@ -4846,40 +4882,40 @@
         <v>15</v>
       </c>
       <c r="C81">
-        <v>7.26</v>
+        <v>208.89</v>
       </c>
       <c r="D81" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E81" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F81" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G81">
-        <v>8.65</v>
+        <v>211</v>
       </c>
       <c r="H81" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I81">
-        <v>7.31</v>
+        <v>191.14</v>
       </c>
       <c r="J81">
-        <v>5.93</v>
+        <v>191.14</v>
       </c>
       <c r="K81">
-        <v>8.65</v>
+        <v>211</v>
       </c>
       <c r="L81">
+        <v>4</v>
+      </c>
+      <c r="M81">
         <v>13</v>
       </c>
-      <c r="M81">
-        <v>17</v>
-      </c>
       <c r="N81">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
@@ -4890,7 +4926,7 @@
         <v>15</v>
       </c>
       <c r="C82">
-        <v>140.63999999999999</v>
+        <v>45.81</v>
       </c>
       <c r="D82" t="s">
         <v>21</v>
@@ -4899,31 +4935,31 @@
         <v>17</v>
       </c>
       <c r="F82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G82">
-        <v>137.07</v>
+        <v>50.65</v>
       </c>
       <c r="H82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I82">
-        <v>194.64</v>
+        <v>45.83</v>
       </c>
       <c r="J82">
-        <v>137.07</v>
+        <v>45.05</v>
       </c>
       <c r="K82">
-        <v>194.64</v>
+        <v>50.65</v>
       </c>
       <c r="L82">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M82">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N82">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
@@ -4934,40 +4970,40 @@
         <v>15</v>
       </c>
       <c r="C83">
-        <v>325.91000000000003</v>
+        <v>7.18</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E83" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G83">
-        <v>314.95</v>
+        <v>8.65</v>
       </c>
       <c r="H83" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I83">
-        <v>368.17</v>
+        <v>7.31</v>
       </c>
       <c r="J83">
-        <v>314.95</v>
+        <v>5.93</v>
       </c>
       <c r="K83">
-        <v>368.17</v>
+        <v>8.65</v>
       </c>
       <c r="L83">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="M83">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="N83">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -4978,40 +5014,40 @@
         <v>15</v>
       </c>
       <c r="C84">
-        <v>26.05</v>
+        <v>128.66999999999999</v>
       </c>
       <c r="D84" t="s">
         <v>21</v>
       </c>
       <c r="E84" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F84" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G84">
-        <v>34.25</v>
+        <v>148.55000000000001</v>
       </c>
       <c r="H84" t="s">
         <v>18</v>
       </c>
       <c r="I84">
-        <v>25.3</v>
+        <v>137.07</v>
       </c>
       <c r="J84">
-        <v>25.3</v>
+        <v>119.62</v>
       </c>
       <c r="K84">
-        <v>34.25</v>
+        <v>148.55000000000001</v>
       </c>
       <c r="L84">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M84">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="N84">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
@@ -5022,40 +5058,40 @@
         <v>15</v>
       </c>
       <c r="C85">
-        <v>126.79</v>
+        <v>351.2</v>
       </c>
       <c r="D85" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E85" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G85">
-        <v>138.9</v>
+        <v>314.95</v>
       </c>
       <c r="H85" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I85">
-        <v>106.37</v>
+        <v>368.17</v>
       </c>
       <c r="J85">
-        <v>106.37</v>
+        <v>314.95</v>
       </c>
       <c r="K85">
-        <v>136.1</v>
+        <v>368.17</v>
       </c>
       <c r="L85">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="M85">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N85">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -5066,40 +5102,40 @@
         <v>15</v>
       </c>
       <c r="C86">
-        <v>20.09</v>
+        <v>25.74</v>
       </c>
       <c r="D86" t="s">
         <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F86" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G86">
-        <v>24.73</v>
+        <v>25.32</v>
       </c>
       <c r="H86" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="I86">
-        <v>20.93</v>
+        <v>34.25</v>
       </c>
       <c r="J86">
-        <v>17.739999999999998</v>
+        <v>25.32</v>
       </c>
       <c r="K86">
-        <v>24.73</v>
+        <v>34.25</v>
       </c>
       <c r="L86">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="M86">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="N86">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
@@ -5110,37 +5146,37 @@
         <v>15</v>
       </c>
       <c r="C87">
-        <v>8.66</v>
+        <v>131.68</v>
       </c>
       <c r="D87" t="s">
         <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F87" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G87">
-        <v>8.48</v>
+        <v>124.81</v>
       </c>
       <c r="H87" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I87">
-        <v>11.3</v>
+        <v>138.9</v>
       </c>
       <c r="J87">
-        <v>8.48</v>
+        <v>124.81</v>
       </c>
       <c r="K87">
-        <v>11.3</v>
+        <v>136.1</v>
       </c>
       <c r="L87">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M87">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N87">
         <v>12</v>
@@ -5154,7 +5190,7 @@
         <v>15</v>
       </c>
       <c r="C88">
-        <v>8.83</v>
+        <v>18.86</v>
       </c>
       <c r="D88" t="s">
         <v>21</v>
@@ -5166,28 +5202,28 @@
         <v>19</v>
       </c>
       <c r="G88">
-        <v>11.81</v>
+        <v>24.73</v>
       </c>
       <c r="H88" t="s">
         <v>18</v>
       </c>
       <c r="I88">
-        <v>8.86</v>
+        <v>20.93</v>
       </c>
       <c r="J88">
-        <v>8.35</v>
+        <v>17.739999999999998</v>
       </c>
       <c r="K88">
-        <v>11.81</v>
+        <v>24.73</v>
       </c>
       <c r="L88">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M88">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N88">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -5198,40 +5234,40 @@
         <v>15</v>
       </c>
       <c r="C89">
-        <v>195.34</v>
+        <v>8.18</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E89" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F89" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G89">
-        <v>189.33</v>
+        <v>9.33</v>
       </c>
       <c r="H89" t="s">
+        <v>18</v>
+      </c>
+      <c r="I89">
+        <v>8.48</v>
+      </c>
+      <c r="J89">
+        <v>7.98</v>
+      </c>
+      <c r="K89">
+        <v>9.33</v>
+      </c>
+      <c r="L89">
         <v>25</v>
       </c>
-      <c r="I89">
-        <v>207.54</v>
-      </c>
-      <c r="J89">
-        <v>189.33</v>
-      </c>
-      <c r="K89">
-        <v>207.54</v>
-      </c>
-      <c r="L89">
-        <v>6</v>
-      </c>
       <c r="M89">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
@@ -5242,7 +5278,7 @@
         <v>15</v>
       </c>
       <c r="C90">
-        <v>16.54</v>
+        <v>8.69</v>
       </c>
       <c r="D90" t="s">
         <v>21</v>
@@ -5251,31 +5287,31 @@
         <v>17</v>
       </c>
       <c r="F90" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G90">
-        <v>16.2</v>
+        <v>11.81</v>
       </c>
       <c r="H90" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I90">
-        <v>22.57</v>
+        <v>8.86</v>
       </c>
       <c r="J90">
-        <v>16.2</v>
+        <v>8.35</v>
       </c>
       <c r="K90">
-        <v>22.57</v>
+        <v>11.81</v>
       </c>
       <c r="L90">
+        <v>15</v>
+      </c>
+      <c r="M90">
         <v>10</v>
       </c>
-      <c r="M90">
-        <v>16</v>
-      </c>
       <c r="N90">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
@@ -5286,40 +5322,40 @@
         <v>15</v>
       </c>
       <c r="C91">
-        <v>20.97</v>
+        <v>199.86</v>
       </c>
       <c r="D91" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F91" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G91">
-        <v>20.48</v>
+        <v>208.05</v>
       </c>
       <c r="H91" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I91">
-        <v>29.11</v>
+        <v>189.33</v>
       </c>
       <c r="J91">
-        <v>20.48</v>
+        <v>189.33</v>
       </c>
       <c r="K91">
-        <v>28.94</v>
+        <v>207.54</v>
       </c>
       <c r="L91">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M91">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N91">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
@@ -5330,7 +5366,7 @@
         <v>15</v>
       </c>
       <c r="C92">
-        <v>81.040000000000006</v>
+        <v>15.84</v>
       </c>
       <c r="D92" t="s">
         <v>21</v>
@@ -5339,31 +5375,31 @@
         <v>17</v>
       </c>
       <c r="F92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G92">
-        <v>107.6</v>
+        <v>16.2</v>
       </c>
       <c r="H92" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I92">
-        <v>80</v>
+        <v>22.57</v>
       </c>
       <c r="J92">
-        <v>80</v>
+        <v>15.3</v>
       </c>
       <c r="K92">
-        <v>107.6</v>
+        <v>22.57</v>
       </c>
       <c r="L92">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M92">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N92">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
@@ -5374,40 +5410,40 @@
         <v>15</v>
       </c>
       <c r="C93">
-        <v>195.93</v>
+        <v>20.21</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E93" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F93" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G93">
-        <v>203.94</v>
+        <v>22.42</v>
       </c>
       <c r="H93" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I93">
-        <v>186.83</v>
+        <v>20.48</v>
       </c>
       <c r="J93">
-        <v>186.83</v>
+        <v>15.31</v>
       </c>
       <c r="K93">
-        <v>203.47</v>
+        <v>22.42</v>
       </c>
       <c r="L93">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="M93">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N93">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
@@ -5418,40 +5454,40 @@
         <v>15</v>
       </c>
       <c r="C94">
-        <v>111.14</v>
+        <v>80.12</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E94" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G94">
-        <v>85.67</v>
+        <v>107.6</v>
       </c>
       <c r="H94" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I94">
-        <v>95.66</v>
+        <v>80</v>
       </c>
       <c r="J94">
-        <v>87</v>
+        <v>76.25</v>
       </c>
       <c r="K94">
-        <v>117.46</v>
+        <v>107.6</v>
       </c>
       <c r="L94">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="M94">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N94">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -5462,40 +5498,40 @@
         <v>15</v>
       </c>
       <c r="C95">
-        <v>326.35000000000002</v>
+        <v>197.22</v>
       </c>
       <c r="D95" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E95" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F95" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G95">
-        <v>284.39999999999998</v>
+        <v>192.59</v>
       </c>
       <c r="H95" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I95">
-        <v>341</v>
+        <v>203.94</v>
       </c>
       <c r="J95">
-        <v>294</v>
+        <v>192.59</v>
       </c>
       <c r="K95">
-        <v>341</v>
+        <v>203.47</v>
       </c>
       <c r="L95">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="M95">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N95">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
@@ -5506,40 +5542,40 @@
         <v>15</v>
       </c>
       <c r="C96">
-        <v>628.94000000000005</v>
+        <v>108.73</v>
       </c>
       <c r="D96" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E96" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F96" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G96">
-        <v>564</v>
+        <v>115.72</v>
       </c>
       <c r="H96" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I96">
-        <v>757.8</v>
+        <v>85.67</v>
       </c>
       <c r="J96">
-        <v>564</v>
+        <v>87</v>
       </c>
       <c r="K96">
-        <v>755.52</v>
+        <v>115.72</v>
       </c>
       <c r="L96">
         <v>9</v>
       </c>
       <c r="M96">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="N96">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
@@ -5550,40 +5586,40 @@
         <v>15</v>
       </c>
       <c r="C97">
-        <v>53.95</v>
+        <v>310.52</v>
       </c>
       <c r="D97" t="s">
         <v>21</v>
       </c>
       <c r="E97" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F97" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G97">
-        <v>51.72</v>
+        <v>337</v>
       </c>
       <c r="H97" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I97">
-        <v>56.37</v>
+        <v>284.39999999999998</v>
       </c>
       <c r="J97">
-        <v>51.72</v>
+        <v>294</v>
       </c>
       <c r="K97">
-        <v>56.37</v>
+        <v>337</v>
       </c>
       <c r="L97">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="M97">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N97">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -5594,40 +5630,40 @@
         <v>15</v>
       </c>
       <c r="C98">
-        <v>18.78</v>
+        <v>621.35</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F98" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G98">
-        <v>17.079999999999998</v>
+        <v>672.64</v>
       </c>
       <c r="H98" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I98">
-        <v>19.190000000000001</v>
+        <v>564</v>
       </c>
       <c r="J98">
-        <v>17.079999999999998</v>
+        <v>564</v>
       </c>
       <c r="K98">
-        <v>18.8</v>
+        <v>672.64</v>
       </c>
       <c r="L98">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="M98">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="N98">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -5638,40 +5674,40 @@
         <v>15</v>
       </c>
       <c r="C99">
-        <v>754.95</v>
+        <v>53.17</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F99" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G99">
-        <v>739.51</v>
+        <v>51.72</v>
       </c>
       <c r="H99" t="s">
         <v>19</v>
       </c>
       <c r="I99">
-        <v>752.41</v>
+        <v>56.37</v>
       </c>
       <c r="J99">
-        <v>739.51</v>
+        <v>51.72</v>
       </c>
       <c r="K99">
-        <v>758.45</v>
+        <v>56.37</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M99">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
@@ -5682,40 +5718,40 @@
         <v>15</v>
       </c>
       <c r="C100">
-        <v>28.31</v>
+        <v>18.39</v>
       </c>
       <c r="D100" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E100" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F100" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G100">
-        <v>25.41</v>
+        <v>19.739999999999998</v>
       </c>
       <c r="H100" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I100">
-        <v>36.799999999999997</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="J100">
-        <v>26.06</v>
+        <v>17.079999999999998</v>
       </c>
       <c r="K100">
-        <v>36.799999999999997</v>
+        <v>18.8</v>
       </c>
       <c r="L100">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="M100">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N100">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
@@ -5726,40 +5762,40 @@
         <v>15</v>
       </c>
       <c r="C101">
-        <v>9.0399999999999991</v>
+        <v>750.9</v>
       </c>
       <c r="D101" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E101" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F101" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G101">
-        <v>8.5500000000000007</v>
+        <v>755.42</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I101">
-        <v>11.85</v>
+        <v>739.51</v>
       </c>
       <c r="J101">
-        <v>8.5500000000000007</v>
+        <v>739.51</v>
       </c>
       <c r="K101">
-        <v>11.85</v>
+        <v>755.42</v>
       </c>
       <c r="L101">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N101">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -5770,40 +5806,40 @@
         <v>15</v>
       </c>
       <c r="C102">
-        <v>401.94</v>
+        <v>27.77</v>
       </c>
       <c r="D102" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E102" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F102" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G102">
-        <v>396.59</v>
+        <v>29.12</v>
       </c>
       <c r="H102" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I102">
-        <v>414.62</v>
+        <v>25.41</v>
       </c>
       <c r="J102">
-        <v>396.59</v>
+        <v>26.06</v>
       </c>
       <c r="K102">
-        <v>414.62</v>
+        <v>29.12</v>
       </c>
       <c r="L102">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="M102">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="N102">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
@@ -5814,7 +5850,7 @@
         <v>15</v>
       </c>
       <c r="C103">
-        <v>1915.92</v>
+        <v>8.48</v>
       </c>
       <c r="D103" t="s">
         <v>21</v>
@@ -5823,31 +5859,28 @@
         <v>17</v>
       </c>
       <c r="F103" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G103">
-        <v>1485.02</v>
+        <v>9.24</v>
       </c>
       <c r="H103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I103">
-        <v>2280.8000000000002</v>
-      </c>
-      <c r="J103">
-        <v>1514.36</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="K103">
-        <v>2280.8000000000002</v>
+        <v>9.24</v>
       </c>
       <c r="L103">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M103">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N103">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -5858,40 +5891,40 @@
         <v>15</v>
       </c>
       <c r="C104">
-        <v>10.54</v>
+        <v>403.79</v>
       </c>
       <c r="D104" t="s">
         <v>16</v>
       </c>
       <c r="E104" t="s">
+        <v>27</v>
+      </c>
+      <c r="F104" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104">
+        <v>396.59</v>
+      </c>
+      <c r="H104" t="s">
         <v>29</v>
       </c>
-      <c r="F104" t="s">
-        <v>30</v>
-      </c>
-      <c r="G104">
-        <v>10.33</v>
-      </c>
-      <c r="H104" t="s">
-        <v>25</v>
-      </c>
       <c r="I104">
-        <v>11.15</v>
+        <v>414.62</v>
       </c>
       <c r="J104">
-        <v>10.33</v>
+        <v>396.59</v>
       </c>
       <c r="K104">
-        <v>11.15</v>
+        <v>414.62</v>
       </c>
       <c r="L104">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="M104">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="N104">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
@@ -5902,40 +5935,40 @@
         <v>15</v>
       </c>
       <c r="C105">
-        <v>1.39</v>
+        <v>1764</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E105" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F105" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G105">
-        <v>1.31</v>
+        <v>1952.59</v>
       </c>
       <c r="H105" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I105">
-        <v>1.87</v>
+        <v>1485.02</v>
       </c>
       <c r="J105">
-        <v>1.31</v>
+        <v>1514.36</v>
       </c>
       <c r="K105">
-        <v>1.85</v>
+        <v>1952.59</v>
       </c>
       <c r="L105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M105">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="N105">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
@@ -5946,40 +5979,40 @@
         <v>15</v>
       </c>
       <c r="C106">
-        <v>87.48</v>
+        <v>10.43</v>
       </c>
       <c r="D106" t="s">
         <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F106" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G106">
-        <v>84.74</v>
+        <v>10.67</v>
       </c>
       <c r="H106" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I106">
-        <v>91.33</v>
+        <v>10.33</v>
       </c>
       <c r="J106">
-        <v>84.74</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="K106">
-        <v>91.33</v>
+        <v>10.67</v>
       </c>
       <c r="L106">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="M106">
         <v>2</v>
       </c>
       <c r="N106">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
@@ -5990,40 +6023,40 @@
         <v>15</v>
       </c>
       <c r="C107">
-        <v>910.34</v>
+        <v>1.3</v>
       </c>
       <c r="D107" t="s">
         <v>21</v>
       </c>
       <c r="E107" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F107" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G107">
-        <v>786.01</v>
+        <v>1.31</v>
       </c>
       <c r="H107" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I107">
-        <v>998.49</v>
+        <v>1.87</v>
       </c>
       <c r="J107">
-        <v>801.32</v>
+        <v>0.95</v>
       </c>
       <c r="K107">
-        <v>998.49</v>
+        <v>1.85</v>
       </c>
       <c r="L107">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M107">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
@@ -6034,40 +6067,40 @@
         <v>15</v>
       </c>
       <c r="C108">
-        <v>58.23</v>
+        <v>88.55</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E108" t="s">
+        <v>34</v>
+      </c>
+      <c r="F108" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108">
+        <v>84.74</v>
+      </c>
+      <c r="H108" t="s">
+        <v>19</v>
+      </c>
+      <c r="I108">
+        <v>91.33</v>
+      </c>
+      <c r="J108">
+        <v>84.74</v>
+      </c>
+      <c r="K108">
+        <v>91.33</v>
+      </c>
+      <c r="L108">
         <v>29</v>
       </c>
-      <c r="F108" t="s">
-        <v>30</v>
-      </c>
-      <c r="G108">
-        <v>56.06</v>
-      </c>
-      <c r="H108" t="s">
-        <v>25</v>
-      </c>
-      <c r="I108">
-        <v>63.11</v>
-      </c>
-      <c r="J108">
-        <v>56.06</v>
-      </c>
-      <c r="K108">
-        <v>62</v>
-      </c>
-      <c r="L108">
-        <v>10</v>
-      </c>
       <c r="M108">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N108">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
@@ -6078,40 +6111,40 @@
         <v>15</v>
       </c>
       <c r="C109">
-        <v>359.6</v>
+        <v>881.64</v>
       </c>
       <c r="D109" t="s">
         <v>21</v>
       </c>
       <c r="E109" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" t="s">
+        <v>19</v>
+      </c>
+      <c r="G109">
+        <v>937.54</v>
+      </c>
+      <c r="H109" t="s">
+        <v>18</v>
+      </c>
+      <c r="I109">
+        <v>786.01</v>
+      </c>
+      <c r="J109">
+        <v>801.32</v>
+      </c>
+      <c r="K109">
+        <v>937.54</v>
+      </c>
+      <c r="L109">
+        <v>7</v>
+      </c>
+      <c r="M109">
         <v>24</v>
       </c>
-      <c r="F109" t="s">
-        <v>18</v>
-      </c>
-      <c r="G109">
-        <v>328.28</v>
-      </c>
-      <c r="H109" t="s">
-        <v>25</v>
-      </c>
-      <c r="I109">
-        <v>487.91</v>
-      </c>
-      <c r="J109">
-        <v>340.34</v>
-      </c>
-      <c r="K109">
-        <v>487.91</v>
-      </c>
-      <c r="L109">
-        <v>5</v>
-      </c>
-      <c r="M109">
-        <v>30</v>
-      </c>
       <c r="N109">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
@@ -6122,40 +6155,40 @@
         <v>15</v>
       </c>
       <c r="C110">
-        <v>385.8</v>
+        <v>57.42</v>
       </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E110" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F110" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G110">
-        <v>356.95</v>
+        <v>62.95</v>
       </c>
       <c r="H110" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I110">
-        <v>449.84</v>
+        <v>56.06</v>
       </c>
       <c r="J110">
-        <v>356.95</v>
+        <v>47.12</v>
       </c>
       <c r="K110">
-        <v>449.84</v>
+        <v>62</v>
       </c>
       <c r="L110">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M110">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="N110">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -6166,40 +6199,40 @@
         <v>15</v>
       </c>
       <c r="C111">
-        <v>407.76</v>
+        <v>355.76</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F111" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G111">
-        <v>389.3</v>
+        <v>385</v>
       </c>
       <c r="H111" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I111">
-        <v>432.86</v>
+        <v>328.28</v>
       </c>
       <c r="J111">
-        <v>389.3</v>
+        <v>340.34</v>
       </c>
       <c r="K111">
-        <v>432.86</v>
+        <v>385</v>
       </c>
       <c r="L111">
         <v>7</v>
       </c>
       <c r="M111">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="N111">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
@@ -6210,40 +6243,40 @@
         <v>15</v>
       </c>
       <c r="C112">
-        <v>434.11</v>
+        <v>399.32</v>
       </c>
       <c r="D112" t="s">
         <v>16</v>
       </c>
       <c r="E112" t="s">
+        <v>27</v>
+      </c>
+      <c r="F112" t="s">
+        <v>28</v>
+      </c>
+      <c r="G112">
+        <v>356.95</v>
+      </c>
+      <c r="H112" t="s">
         <v>29</v>
       </c>
-      <c r="F112" t="s">
-        <v>30</v>
-      </c>
-      <c r="G112">
-        <v>428.11</v>
-      </c>
-      <c r="H112" t="s">
-        <v>25</v>
-      </c>
       <c r="I112">
-        <v>479</v>
+        <v>449.84</v>
       </c>
       <c r="J112">
-        <v>428.11</v>
+        <v>356.95</v>
       </c>
       <c r="K112">
-        <v>479</v>
+        <v>449.84</v>
       </c>
       <c r="L112">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="M112">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N112">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
@@ -6254,40 +6287,40 @@
         <v>15</v>
       </c>
       <c r="C113">
-        <v>18.809999999999999</v>
+        <v>396.33</v>
       </c>
       <c r="D113" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E113" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F113" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G113">
-        <v>19.48</v>
+        <v>413.16</v>
       </c>
       <c r="H113" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I113">
-        <v>25.94</v>
+        <v>389.3</v>
       </c>
       <c r="J113">
-        <v>18.09</v>
+        <v>389.3</v>
       </c>
       <c r="K113">
-        <v>25.94</v>
+        <v>413.16</v>
       </c>
       <c r="L113">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M113">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N113">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -6298,40 +6331,40 @@
         <v>15</v>
       </c>
       <c r="C114">
-        <v>0.83</v>
+        <v>421.85</v>
       </c>
       <c r="D114" t="s">
         <v>21</v>
       </c>
       <c r="E114" t="s">
+        <v>34</v>
+      </c>
+      <c r="F114" t="s">
+        <v>19</v>
+      </c>
+      <c r="G114">
+        <v>447.69</v>
+      </c>
+      <c r="H114" t="s">
+        <v>28</v>
+      </c>
+      <c r="I114">
+        <v>428.11</v>
+      </c>
+      <c r="J114">
+        <v>419.19</v>
+      </c>
+      <c r="K114">
+        <v>447.69</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="M114">
         <v>24</v>
       </c>
-      <c r="F114" t="s">
-        <v>30</v>
-      </c>
-      <c r="G114">
-        <v>0.76</v>
-      </c>
-      <c r="H114" t="s">
-        <v>19</v>
-      </c>
-      <c r="I114">
-        <v>0.96</v>
-      </c>
-      <c r="J114">
-        <v>0.76</v>
-      </c>
-      <c r="K114">
-        <v>0.96</v>
-      </c>
-      <c r="L114">
-        <v>35</v>
-      </c>
-      <c r="M114">
-        <v>4</v>
-      </c>
       <c r="N114">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
@@ -6342,37 +6375,37 @@
         <v>15</v>
       </c>
       <c r="C115">
-        <v>318.86</v>
+        <v>18.579999999999998</v>
       </c>
       <c r="D115" t="s">
+        <v>21</v>
+      </c>
+      <c r="E115" t="s">
+        <v>34</v>
+      </c>
+      <c r="F115" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115">
+        <v>19.48</v>
+      </c>
+      <c r="H115" t="s">
+        <v>19</v>
+      </c>
+      <c r="I115">
+        <v>25.94</v>
+      </c>
+      <c r="J115">
+        <v>13.21</v>
+      </c>
+      <c r="K115">
+        <v>25.94</v>
+      </c>
+      <c r="L115">
+        <v>14</v>
+      </c>
+      <c r="M115">
         <v>16</v>
-      </c>
-      <c r="E115" t="s">
-        <v>17</v>
-      </c>
-      <c r="F115" t="s">
-        <v>18</v>
-      </c>
-      <c r="G115">
-        <v>287.11</v>
-      </c>
-      <c r="H115" t="s">
-        <v>19</v>
-      </c>
-      <c r="I115">
-        <v>337.23</v>
-      </c>
-      <c r="J115">
-        <v>294.3</v>
-      </c>
-      <c r="K115">
-        <v>337.23</v>
-      </c>
-      <c r="L115">
-        <v>13</v>
-      </c>
-      <c r="M115">
-        <v>27</v>
       </c>
       <c r="N115">
         <v>3</v>
@@ -6386,40 +6419,40 @@
         <v>15</v>
       </c>
       <c r="C116">
-        <v>158.86000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="D116" t="s">
         <v>21</v>
       </c>
       <c r="E116" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F116" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G116">
-        <v>148.5</v>
+        <v>0.86</v>
       </c>
       <c r="H116" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I116">
-        <v>171.35</v>
+        <v>0.76</v>
       </c>
       <c r="J116">
-        <v>148.5</v>
+        <v>0.74</v>
       </c>
       <c r="K116">
-        <v>168.15</v>
+        <v>0.86</v>
       </c>
       <c r="L116">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="M116">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N116">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
@@ -6430,40 +6463,40 @@
         <v>15</v>
       </c>
       <c r="C117">
-        <v>582.59</v>
+        <v>302.91000000000003</v>
       </c>
       <c r="D117" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E117" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F117" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G117">
-        <v>510.37</v>
+        <v>338.88</v>
       </c>
       <c r="H117" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I117">
-        <v>663.98</v>
+        <v>287.11</v>
       </c>
       <c r="J117">
-        <v>510.37</v>
+        <v>294.3</v>
       </c>
       <c r="K117">
-        <v>663.98</v>
+        <v>337.23</v>
       </c>
       <c r="L117">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M117">
         <v>27</v>
       </c>
       <c r="N117">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
@@ -6474,40 +6507,40 @@
         <v>15</v>
       </c>
       <c r="C118">
-        <v>3.37</v>
+        <v>159.66999999999999</v>
       </c>
       <c r="D118" t="s">
+        <v>21</v>
+      </c>
+      <c r="E118" t="s">
+        <v>17</v>
+      </c>
+      <c r="F118" t="s">
+        <v>19</v>
+      </c>
+      <c r="G118">
+        <v>161.18</v>
+      </c>
+      <c r="H118" t="s">
+        <v>18</v>
+      </c>
+      <c r="I118">
+        <v>148.5</v>
+      </c>
+      <c r="J118">
+        <v>148.5</v>
+      </c>
+      <c r="K118">
+        <v>161.18</v>
+      </c>
+      <c r="L118">
+        <v>9</v>
+      </c>
+      <c r="M118">
+        <v>6</v>
+      </c>
+      <c r="N118">
         <v>16</v>
-      </c>
-      <c r="E118" t="s">
-        <v>24</v>
-      </c>
-      <c r="F118" t="s">
-        <v>25</v>
-      </c>
-      <c r="G118">
-        <v>3.75</v>
-      </c>
-      <c r="H118" t="s">
-        <v>18</v>
-      </c>
-      <c r="I118">
-        <v>3.03</v>
-      </c>
-      <c r="J118">
-        <v>3.06</v>
-      </c>
-      <c r="K118">
-        <v>3.75</v>
-      </c>
-      <c r="L118">
-        <v>3</v>
-      </c>
-      <c r="M118">
-        <v>17</v>
-      </c>
-      <c r="N118">
-        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
@@ -6518,40 +6551,128 @@
         <v>15</v>
       </c>
       <c r="C119">
-        <v>55.08</v>
+        <v>566.09</v>
       </c>
       <c r="D119" t="s">
+        <v>21</v>
+      </c>
+      <c r="E119" t="s">
+        <v>17</v>
+      </c>
+      <c r="F119" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119">
+        <v>601.5</v>
+      </c>
+      <c r="H119" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119">
+        <v>510.37</v>
+      </c>
+      <c r="J119">
+        <v>510.37</v>
+      </c>
+      <c r="K119">
+        <v>601.5</v>
+      </c>
+      <c r="L119">
+        <v>7</v>
+      </c>
+      <c r="M119">
+        <v>27</v>
+      </c>
+      <c r="N119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>142</v>
+      </c>
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120">
+        <v>3.58</v>
+      </c>
+      <c r="D120" t="s">
         <v>16</v>
       </c>
-      <c r="E119" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" t="s">
-        <v>25</v>
-      </c>
-      <c r="G119">
+      <c r="E120" t="s">
+        <v>27</v>
+      </c>
+      <c r="F120" t="s">
+        <v>28</v>
+      </c>
+      <c r="G120">
+        <v>3.26</v>
+      </c>
+      <c r="H120" t="s">
+        <v>29</v>
+      </c>
+      <c r="I120">
+        <v>3.75</v>
+      </c>
+      <c r="J120">
+        <v>3.26</v>
+      </c>
+      <c r="K120">
+        <v>3.75</v>
+      </c>
+      <c r="L120">
+        <v>5</v>
+      </c>
+      <c r="M120">
+        <v>19</v>
+      </c>
+      <c r="N120">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>143</v>
+      </c>
+      <c r="B121" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121">
+        <v>56.66</v>
+      </c>
+      <c r="D121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121" t="s">
+        <v>27</v>
+      </c>
+      <c r="F121" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121">
+        <v>54.36</v>
+      </c>
+      <c r="H121" t="s">
+        <v>29</v>
+      </c>
+      <c r="I121">
         <v>56.04</v>
       </c>
-      <c r="H119" t="s">
-        <v>18</v>
-      </c>
-      <c r="I119">
-        <v>52.62</v>
-      </c>
-      <c r="J119">
-        <v>52.62</v>
-      </c>
-      <c r="K119">
-        <v>56.04</v>
-      </c>
-      <c r="L119">
-        <v>3</v>
-      </c>
-      <c r="M119">
-        <v>17</v>
-      </c>
-      <c r="N119">
+      <c r="J121">
+        <v>54.36</v>
+      </c>
+      <c r="K121">
+        <v>58.62</v>
+      </c>
+      <c r="L121">
         <v>5</v>
+      </c>
+      <c r="M121">
+        <v>18</v>
+      </c>
+      <c r="N121">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
